--- a/plantillas/79.xlsx
+++ b/plantillas/79.xlsx
@@ -27,7 +27,7 @@
     <definedName name="MARCA_13">Listas!$P$2:$P$15</definedName>
     <definedName name="MARCA_14">Listas!$Q$2:$Q$4</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$12</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$8</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$9</definedName>
     <definedName name="MARCA_17">Listas!$T$2:$T$12</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$7</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$10</definedName>
@@ -53,7 +53,7 @@
     <definedName name="MARCA_39">Listas!$AP$2:$AP$36</definedName>
     <definedName name="MARCA_40">Listas!$AQ$2:$AQ$11</definedName>
     <definedName name="MARCA_41">Listas!$AR$2:$AR$7</definedName>
-    <definedName name="MARCA_42">Listas!$AS$2:$AS$54</definedName>
+    <definedName name="MARCA_42">Listas!$AS$2:$AS$53</definedName>
     <definedName name="MARCA_43">Listas!$AT$2:$AT$7</definedName>
     <definedName name="MARCA_44">Listas!$AU$2:$AU$10</definedName>
     <definedName name="MARCA_45">Listas!$AV$2:$AV$13</definedName>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EUK DOG LARGE PUPPY 3 Kg (6.61 lbs) · 90018520000</t>
+          <t>EUK DOG LARGE ADULT  15 kg (33.06 lbs) · 90018610000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
+          <t>EUK DOG LARGE PUPPY 3 Kg (6.61 lbs) · 90018520000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
+          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
+          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL ADULT  7.5 Kg (16.53 lbs) · 90018560000</t>
+          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL PUPPY 3 Kg (6.61 lbs) · 90018470000</t>
+          <t>EUK DOG SMALL ADULT  7.5 Kg (16.53 lbs) · 90018560000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL SENIOR  3 Kg (6.61 lbs) · 90018620000</t>
+          <t>EUK DOG SMALL PUPPY 3 Kg (6.61 lbs) · 90018470000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -10424,6 +10424,11 @@
           <t>PA VITAMINA EN GEL CALORIAS P/PERRO · 90330290000</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>EUK DOG SMALL SENIOR  3 Kg (6.61 lbs) · 90018620000</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>EN SNACK TROPICAL P/ROEDORES · 93500000278</t>
@@ -11420,7 +11425,7 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -11517,7 +11522,7 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -11614,7 +11619,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -11706,7 +11711,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -11793,7 +11798,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -11875,7 +11880,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -11952,7 +11957,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -12019,7 +12024,7 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP PROPLAN ADULTO RZ MD 13KG · 93520220000</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -12081,7 +12086,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO RZ MD 13KG · 93520220000</t>
+          <t>PP PROPLAN ADULTO SENSIBLE MD 3KG · 93520140000</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -12143,7 +12148,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO SENSIBLE MD 3KG · 93520140000</t>
+          <t>PP PROPLAN BAJO EN CALORIAS 3KG · 93520240000</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -12205,7 +12210,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>PP PROPLAN BAJO EN CALORIAS 3KG · 93520240000</t>
+          <t>PP PROPLAN CACHORRO RZ GDE 13KG · 93520210000</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -12267,7 +12272,7 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ GDE 13KG · 93520210000</t>
+          <t>PP PROPLAN CACHORRO RZ MD 13KG · 93520200000</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -12329,7 +12334,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ MD 13KG · 93520200000</t>
+          <t>PP PROPLAN CACHORRO RZ MD 7.5KG · 93520190000</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -12391,7 +12396,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ MD 7.5KG · 93520190000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -12453,7 +12458,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 7.5KG · 93520180000</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -12510,7 +12515,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ PQNA 7.5KG · 93520180000</t>
+          <t>PP PROPLAN CACHORROS POUCH 85 G · 93520260000</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -12567,7 +12572,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS POUCH 85 G · 93520260000</t>
+          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -12624,7 +12629,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
+          <t>PP PROPLAN GATITO POLLO/ARROZ 1.5KG · 93520250000</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -12676,7 +12681,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>PP PROPLAN GATITO POLLO/ARROZ 1.5KG · 93520250000</t>
+          <t>PP PROPLAN MENTE ACTIVA RZ MD 3KG · 93520230000</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -12728,7 +12733,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>PP PROPLAN MENTE ACTIVA RZ MD 3KG · 93520230000</t>
+          <t>PP PROPLAN RZ MD Y GDE OPTIFIT 13KG · 93520150000</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -12780,7 +12785,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>PP PROPLAN RZ MD Y GDE OPTIFIT 13KG · 93520150000</t>
+          <t>PP SENIOR  ACTIVE MIND RZ MEDIANA 13KG · 93501261000</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -12827,7 +12832,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ MEDIANA 13KG · 93501261000</t>
+          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -12874,7 +12879,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
+          <t>PP SENIOR ACTIVE MIND RZ PEQUENA 7.5KG · 93505971000</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -12921,7 +12926,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>PP SENIOR ACTIVE MIND RZ PEQUENA 7.5KG · 93505971000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -12968,7 +12973,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -13015,7 +13020,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -13052,7 +13057,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -13089,7 +13094,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PROPLAN ADULTO EXIGENTE RZ PQNA 3KG · 93520060000</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -13121,7 +13126,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO EXIGENTE RZ PQNA 3KG · 93520060000</t>
+          <t>PROPLAN ADULTO RZ MD OPTIHEALTH 7.5 · 93520070000</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -13153,7 +13158,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MD OPTIHEALTH 7.5 · 93520070000</t>
+          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -13185,7 +13190,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
+          <t>PROPLAN EXIGENT BOCADOS PEQUENOS 1KG MX · 90038580000</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -13217,7 +13222,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>PROPLAN EXIGENT BOCADOS PEQUENOS 1KG MX · 90038580000</t>
+          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -13244,7 +13249,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
+          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -13271,7 +13276,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
+          <t>PROPLAN MENTE ACTIVA BOCADOS PEQ 1KG MX · 90038610000</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -13298,7 +13303,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>PROPLAN MENTE ACTIVA BOCADOS PEQ 1KG MX · 90038610000</t>
+          <t>PROPLAN OPTIDERMA RZ PQNA 7.5KG · 93520010000</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -13325,7 +13330,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>PROPLAN OPTIDERMA RZ PQNA 7.5KG · 93520010000</t>
+          <t>PROPLAN PIEL SENSI ADULTO RAZAS PEQ 1KG · 90038600000</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13352,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>PROPLAN PIEL SENSI ADULTO RAZAS PEQ 1KG · 90038600000</t>
+          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13374,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
     </row>
@@ -13387,11 +13392,6 @@
       <c r="AK54" t="inlineStr">
         <is>
           <t>NS PERRO GF POLLO GUISANTE 12LB · 93500000441</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr">
-        <is>
-          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17758,16 +17758,16 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>EUK DOG LARGE PUPPY 3 Kg (6.61 lbs) · 90018520000</t>
+          <t>EUK DOG LARGE ADULT  15 kg (33.06 lbs) · 90018610000</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>90018520000</t>
+          <t>90018610000</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17778,16 +17778,16 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
+          <t>EUK DOG LARGE PUPPY 3 Kg (6.61 lbs) · 90018520000</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>90018570000</t>
+          <t>90018520000</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17798,16 +17798,16 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
+          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>90018490000</t>
+          <t>90018570000</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17818,16 +17818,16 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
+          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>90018630000</t>
+          <t>90018490000</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17838,16 +17838,16 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL ADULT  7.5 Kg (16.53 lbs) · 90018560000</t>
+          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>90018560000</t>
+          <t>90018630000</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17858,16 +17858,16 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL PUPPY 3 Kg (6.61 lbs) · 90018470000</t>
+          <t>EUK DOG SMALL ADULT  7.5 Kg (16.53 lbs) · 90018560000</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>90018470000</t>
+          <t>90018560000</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17878,12 +17878,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL SENIOR  3 Kg (6.61 lbs) · 90018620000</t>
+          <t>EUK DOG SMALL PUPPY 3 Kg (6.61 lbs) · 90018470000</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>90018620000</t>
+          <t>90018470000</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -17898,36 +17898,36 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>EN SANCKS DE VEGETALES P/ROEDORES · 93500000277</t>
+          <t>EUK DOG SMALL SENIOR  3 Kg (6.61 lbs) · 90018620000</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>93500000277</t>
+          <t>90018620000</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>EXOTIC NUTRITION</t>
+          <t>EUKANUBA</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>EN SNACK CAMOTE P/ROEDORES · 93500000285</t>
+          <t>EN SANCKS DE VEGETALES P/ROEDORES · 93500000277</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>93500000285</t>
+          <t>93500000277</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17938,16 +17938,16 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>EN SNACK DE LA ISLA P/ROEDORES · 93500000279</t>
+          <t>EN SNACK CAMOTE P/ROEDORES · 93500000285</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>93500000279</t>
+          <t>93500000285</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17958,16 +17958,16 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>EN SNACK ESCARAMUJOS DE ROSAS · 93500000282</t>
+          <t>EN SNACK DE LA ISLA P/ROEDORES · 93500000279</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>93500000282</t>
+          <t>93500000279</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17978,16 +17978,16 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>EN SNACK MANGO Y PAPAYA P/ROEDORES · 93500000276</t>
+          <t>EN SNACK ESCARAMUJOS DE ROSAS · 93500000282</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>93500000276</t>
+          <t>93500000282</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17998,16 +17998,16 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EN SNACK MEZCLA D FRUTAS P/ROED · 93500000286</t>
+          <t>EN SNACK MANGO Y PAPAYA P/ROEDORES · 93500000276</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>93500000286</t>
+          <t>93500000276</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18018,16 +18018,16 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>EN SNACK TROCITOS DE BANANA P/ROEDORES · 93500000275</t>
+          <t>EN SNACK MEZCLA D FRUTAS P/ROED · 93500000286</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>93500000275</t>
+          <t>93500000286</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18038,16 +18038,16 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>EN SNACK TROPICAL P/ROEDORES · 93500000278</t>
+          <t>EN SNACK TROCITOS DE BANANA P/ROEDORES · 93500000275</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>93500000278</t>
+          <t>93500000275</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18058,16 +18058,16 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EN SNACK VEG E INSECTOS P/ ERIZOS · 93500000283</t>
+          <t>EN SNACK TROPICAL P/ROEDORES · 93500000278</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>93500000283</t>
+          <t>93500000278</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18078,16 +18078,16 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>EN SNACK YOGURT Y MORAS P/ROED · 93500000280</t>
+          <t>EN SNACK VEG E INSECTOS P/ ERIZOS · 93500000283</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>93500000280</t>
+          <t>93500000283</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18098,16 +18098,16 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>EN SNACK YOGURT Y PAPAYA P/ROED · 93500000281</t>
+          <t>EN SNACK YOGURT Y MORAS P/ROED · 93500000280</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>93500000281</t>
+          <t>93500000280</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18118,36 +18118,36 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FANCY FEAST CAZUELA ATUN Y SALMON POUCH · 90038490000</t>
+          <t>EN SNACK YOGURT Y PAPAYA P/ROED · 93500000281</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>90038490000</t>
+          <t>93500000281</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>EXOTIC NUTRITION</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
+          <t>FANCY FEAST CAZUELA ATUN Y SALMON POUCH · 90038490000</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>93509350000</t>
+          <t>90038490000</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18158,16 +18158,16 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FANCY FEAST ESTOFADO CON TUNA POUCH 85G · 90038470000</t>
+          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>90038470000</t>
+          <t>93509350000</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18178,12 +18178,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
+          <t>FANCY FEAST ESTOFADO CON TUNA POUCH 85G · 90038470000</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>90038480000</t>
+          <t>90038470000</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -18198,16 +18198,16 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
+          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>90038500000</t>
+          <t>90038480000</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18218,16 +18218,16 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
+          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>93509370000</t>
+          <t>90038500000</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18238,36 +18238,36 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FELIX CARNE 85G MX · 90038460000</t>
+          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>90038460000</t>
+          <t>93509370000</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>FANCY FEAST</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
+          <t>FELIX CARNE 85G MX · 90038460000</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>90038450000</t>
+          <t>90038460000</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18278,16 +18278,16 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>90038530000</t>
+          <t>90038450000</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18298,16 +18298,16 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>90038540000</t>
+          <t>90038530000</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18318,16 +18318,16 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FELIX GATITOS 500G MX · 90038510000</t>
+          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>90038510000</t>
+          <t>90038540000</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18338,16 +18338,16 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
+          <t>FELIX GATITOS 500G MX · 90038510000</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>93502660000</t>
+          <t>90038510000</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18358,16 +18358,16 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>93502640000</t>
+          <t>93502660000</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18378,16 +18378,16 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>93502650000</t>
+          <t>93502640000</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18398,12 +18398,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FELIX POLLO 85G MX · 90038440000</t>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>90038440000</t>
+          <t>93502650000</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -18418,36 +18418,36 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>GATI MAR Y TIERRA 6.6LB · 93519170000</t>
+          <t>FELIX POLLO 85G MX · 90038440000</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>93519170000</t>
+          <t>90038440000</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>GATI PESCADO 6.6LB · 93519150000</t>
+          <t>GATI MAR Y TIERRA 6.6LB · 93519170000</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>93519150000</t>
+          <t>93519170000</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18458,36 +18458,36 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>GATI PESCADO 6.6LB · 93519150000</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>93519150000</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GATI</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18498,16 +18498,16 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18518,16 +18518,16 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18538,12 +18538,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -18558,36 +18558,36 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO DIGESTIVO 6OZ · 93500000212</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>93500000212</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>GRANDMA LUCY'S</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO INFLAMACION 6OZ · 93500000213</t>
+          <t>D GL SUPLEMENTO DIGESTIVO 6OZ · 93500000212</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>93500000213</t>
+          <t>93500000212</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18598,16 +18598,16 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO PARA VEJIGA 6OZ · 93500000214</t>
+          <t>D GL SUPLEMENTO INFLAMACION 6OZ · 93500000213</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>93500000214</t>
+          <t>93500000213</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18618,16 +18618,16 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO PIEL Y PELAJE 6OZ · 93500000215</t>
+          <t>D GL SUPLEMENTO PARA VEJIGA 6OZ · 93500000214</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>93500000215</t>
+          <t>93500000214</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18638,36 +18638,36 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>D GM GF PERRO COUNT NATURALS CORDERO 4LB · 93500000117</t>
+          <t>D GL SUPLEMENTO PIEL Y PELAJE 6OZ · 93500000215</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>93500000117</t>
+          <t>93500000215</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>GRANDMA MAE'S</t>
+          <t>GRANDMA LUCY'S</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>D GM PERRO COUNT NAT MEZCLA D LA GR 24 · 93500000157</t>
+          <t>D GM GF PERRO COUNT NATURALS CORDERO 4LB · 93500000117</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>93500000157</t>
+          <t>93500000117</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18678,16 +18678,16 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>GM COUNT NAT CORDERO/ PESCADO P PERROS 4 · 93500000134</t>
+          <t>D GM PERRO COUNT NAT MEZCLA D LA GR 24 · 93500000157</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>93500000134</t>
+          <t>93500000157</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18698,16 +18698,16 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>GM COUNT NAT ESTOMAG SENSIBL/ PERRO 12 · 93500000143</t>
+          <t>GM COUNT NAT CORDERO/ PESCADO P PERROS 4 · 93500000134</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>93500000143</t>
+          <t>93500000134</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18718,16 +18718,16 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>GM COUNT NAT PERROS CACHORROS 4LB · 93500000146</t>
+          <t>GM COUNT NAT ESTOMAG SENSIBL/ PERRO 12 · 93500000143</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>93500000146</t>
+          <t>93500000143</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18738,16 +18738,16 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 12 · 93500000139</t>
+          <t>GM COUNT NAT PERROS CACHORROS 4LB · 93500000146</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>93500000139</t>
+          <t>93500000146</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18758,16 +18758,16 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 4L · 93500000138</t>
+          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 12 · 93500000139</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>93500000138</t>
+          <t>93500000139</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18778,12 +18778,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GM GATOS Y GATITOS COUNTRY NATURALS 3 · 93500000169</t>
+          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 4L · 93500000138</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>93500000169</t>
+          <t>93500000138</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -18798,16 +18798,16 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>GM GF PERRO COUNT NATURAL MULTI PROT 4LB · 93500000130</t>
+          <t>GM GATOS Y GATITOS COUNTRY NATURALS 3 · 93500000169</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>93500000130</t>
+          <t>93500000169</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18818,16 +18818,16 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GM GF PERRO COUNTRY NATURALS PAVO 4LB · 93500000109</t>
+          <t>GM GF PERRO COUNT NATURAL MULTI PROT 4LB · 93500000130</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>93500000109</t>
+          <t>93500000130</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18838,16 +18838,16 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>GM PERRO COUNT NATURALS MEZCLA D LA GR 4 · 93500000155</t>
+          <t>GM GF PERRO COUNTRY NATURALS PAVO 4LB · 93500000109</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>93500000155</t>
+          <t>93500000109</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18858,36 +18858,36 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>D ALIM. HIGGINS VITA SEED CANARIO 5LB · 90416500000</t>
+          <t>GM PERRO COUNT NATURALS MEZCLA D LA GR 4 · 93500000155</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>90416500000</t>
+          <t>93500000155</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>GRANDMA MAE'S</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>D ALIM. HIGGINS VITA SEED FINCHE 5LBS · 90416540000</t>
+          <t>D ALIM. HIGGINS VITA SEED CANARIO 5LB · 90416500000</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>90416540000</t>
+          <t>90416500000</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18898,16 +18898,16 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>D HIGGINS INTUNE ALIMENTO CONURO 2LB · 93515860000</t>
+          <t>D ALIM. HIGGINS VITA SEED FINCHE 5LBS · 90416540000</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>93515860000</t>
+          <t>90416540000</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18918,16 +18918,16 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>D HIGGINS SNACK DE HIERBAS 1OZ · 93510470000</t>
+          <t>D HIGGINS INTUNE ALIMENTO CONURO 2LB · 93515860000</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>93510470000</t>
+          <t>93515860000</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18938,16 +18938,16 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>D HIGGINS VITA SEED PERIQ 2.5LB · 90416510000</t>
+          <t>D HIGGINS SNACK DE HIERBAS 1OZ · 93510470000</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>90416510000</t>
+          <t>93510470000</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18958,16 +18958,16 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>D HIGGINS VITA SEED PERIQUITOS 5LB · 90416520000</t>
+          <t>D HIGGINS VITA SEED PERIQ 2.5LB · 90416510000</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>90416520000</t>
+          <t>90416510000</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18978,16 +18978,16 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
+          <t>D HIGGINS VITA SEED PERIQUITOS 5LB · 90416520000</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>93510560000</t>
+          <t>90416520000</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18998,16 +18998,16 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK BOCADOS DE MIJO 1OZ · 93510480000</t>
+          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>93510480000</t>
+          <t>93510560000</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19018,16 +19018,16 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK FRUTAS DE LA ISLA 2.2 · 93510510000</t>
+          <t>HIGGINS SNACK BOCADOS DE MIJO 1OZ · 93510480000</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>93510510000</t>
+          <t>93510480000</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19038,16 +19038,16 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK FRUTAS VEGETALES 5OZ · 93510450000</t>
+          <t>HIGGINS SNACK FRUTAS DE LA ISLA 2.2 · 93510510000</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>93510450000</t>
+          <t>93510510000</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19058,16 +19058,16 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK FRUTAS VEGETALES SM 3 · 93510460000</t>
+          <t>HIGGINS SNACK FRUTAS VEGETALES 5OZ · 93510450000</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>93510460000</t>
+          <t>93510450000</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19078,16 +19078,16 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK P AVES CANTORAS 3 OZ · 93510490000</t>
+          <t>HIGGINS SNACK FRUTAS VEGETALES SM 3 · 93510460000</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>93510490000</t>
+          <t>93510460000</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19098,16 +19098,16 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
+          <t>HIGGINS SNACK P AVES CANTORAS 3 OZ · 93510490000</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>93510430000</t>
+          <t>93510490000</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19118,12 +19118,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
+          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>93510440000</t>
+          <t>93510430000</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -19138,16 +19138,16 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM/HAMSTERS 2.5 · 93518320000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>93518320000</t>
+          <t>93510440000</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19158,16 +19158,16 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST LORO3LB · 90409690000</t>
+          <t>HIGGINS SUNBURST ALIM/HAMSTERS 2.5 · 93518320000</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>90409690000</t>
+          <t>93518320000</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19178,16 +19178,16 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HIGGINS VITA LORO 3LBS · 90739860000</t>
+          <t>HIGGINS SUNBURST LORO3LB · 90409690000</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>90739860000</t>
+          <t>90409690000</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19198,16 +19198,16 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HIGGINS VITA SEED CACATUA 2.5 · 90416550000</t>
+          <t>HIGGINS VITA LORO 3LBS · 90739860000</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>90416550000</t>
+          <t>90739860000</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19218,16 +19218,16 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HIGGINS VITA SEED FINCHE 2LBS · 90416530000</t>
+          <t>HIGGINS VITA SEED CACATUA 2.5 · 90416550000</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>90416530000</t>
+          <t>90416550000</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19238,16 +19238,16 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
+          <t>HIGGINS VITA SEED FINCHE 2LBS · 90416530000</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>90480080000</t>
+          <t>90416530000</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19258,16 +19258,16 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
+          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>93504530000</t>
+          <t>90480080000</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19278,16 +19278,16 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
+          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>93504540000</t>
+          <t>93504530000</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19298,36 +19298,36 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>SD ADULTO 1-6  6.6lb · 93509800001</t>
+          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>93509800001</t>
+          <t>93504540000</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>HILL'S</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>SD ADULTO 1-6 BOCADOS PQNOS 4,4 LB · 93509790001</t>
+          <t>SD ADULTO 1-6  6.6lb · 93509800001</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>93509790001</t>
+          <t>93509800001</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19338,16 +19338,16 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+ BOCADOS PQNOS  4.4 LB · 93506470001</t>
+          <t>SD ADULTO 1-6 BOCADOS PQNOS 4,4 LB · 93509790001</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>93506470001</t>
+          <t>93509790001</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19358,16 +19358,16 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+6.6lb · 93506480001</t>
+          <t>SD ADULTO 7+ BOCADOS PQNOS  4.4 LB · 93506470001</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>93506480001</t>
+          <t>93506470001</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19378,16 +19378,16 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SD ADULTO CORDERO Y ARROZ 15.5LB · 93509870000</t>
+          <t>SD ADULTO 7+6.6lb · 93506480001</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>93509870000</t>
+          <t>93506480001</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19398,16 +19398,16 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SD ADULTO CORDERO Y ARROZ SB 15.5 · 93509810000</t>
+          <t>SD ADULTO CORDERO Y ARROZ 15.5LB · 93509870000</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>93509810000</t>
+          <t>93509870000</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19418,16 +19418,16 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
+          <t>SD ADULTO CORDERO Y ARROZ SB 15.5 · 93509810000</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>93506540000</t>
+          <t>93509810000</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19438,16 +19438,16 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SD ADULTO RAZAS PEQUEÑAS Y TOY 4.5 · 93515520000</t>
+          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>93515520000</t>
+          <t>93506540000</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19458,16 +19458,16 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
+          <t>SD ADULTO RAZAS PEQUEÑAS Y TOY 4.5 · 93515520000</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>93516920000</t>
+          <t>93515520000</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19478,16 +19478,16 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SD ALIMENTO PARA PERRO ADULTO 15LB · 93515020000</t>
+          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>93515020000</t>
+          <t>93516920000</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19498,16 +19498,16 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SD CACHORRO BOCADOS PQN 4.5LB · 93509770000</t>
+          <t>SD ALIMENTO PARA PERRO ADULTO 15LB · 93515020000</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>93509770000</t>
+          <t>93515020000</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19518,16 +19518,16 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
+          <t>SD CACHORRO BOCADOS PQN 4.5LB · 93509770000</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>93515510000</t>
+          <t>93509770000</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19538,16 +19538,16 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SD CANINE CACHORROS 15.5LB · 90304140000</t>
+          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>90304140000</t>
+          <t>93515510000</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19558,16 +19558,16 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SD CANINE PUPPY SM. BITE 12.5LB. · 90402810000</t>
+          <t>SD CANINE CACHORROS 15.5LB · 90304140000</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>90402810000</t>
+          <t>90304140000</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19578,16 +19578,16 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
+          <t>SD CANINE PUPPY SM. BITE 12.5LB. · 90402810000</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>90300090000</t>
+          <t>90402810000</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19598,16 +19598,16 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
+          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>90303640000</t>
+          <t>90300090000</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19618,16 +19618,16 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
+          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>93509830000</t>
+          <t>90303640000</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19638,16 +19638,16 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>SD LATA ADULTO POLLO 13OZ · 93509850000</t>
+          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>93509850000</t>
+          <t>93509830000</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19658,16 +19658,16 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
+          <t>SD LATA ADULTO POLLO 13OZ · 93509850000</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>93509840000</t>
+          <t>93509850000</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19678,36 +19678,36 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE MANI LG · 93518010000</t>
+          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>93518010000</t>
+          <t>93509840000</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>HIMALAYAN</t>
+          <t>HILL'S</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE MANI MD · 93518030000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE MANI LG · 93518010000</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>93518030000</t>
+          <t>93518010000</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19718,16 +19718,16 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE MANI SM · 93518050000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE MANI MD · 93518030000</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>93518050000</t>
+          <t>93518030000</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19738,16 +19738,16 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE POLLO LG · 93518000000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE MANI SM · 93518050000</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>93518000000</t>
+          <t>93518050000</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19758,12 +19758,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE POLLO SM · 93518040000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE POLLO LG · 93518000000</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>93518040000</t>
+          <t>93518000000</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -19778,36 +19778,36 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>D KT ALIM. EXACT CACATUA RB 3LB · 90402560000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE POLLO SM · 93518040000</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>90402560000</t>
+          <t>93518040000</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>HIMALAYAN</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>D KT ALIM. FIESTA MAX CONEJO 6/6.5LB · 90416690000</t>
+          <t>D KT ALIM. EXACT CACATUA RB 3LB · 90402560000</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>90416690000</t>
+          <t>90402560000</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19818,16 +19818,16 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>D KT ALIMENTO PARA KOI 25LB · 93500000264</t>
+          <t>D KT ALIM. FIESTA MAX CONEJO 6/6.5LB · 90416690000</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>93500000264</t>
+          <t>90416690000</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19838,16 +19838,16 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>D KT BARRA DE SEMILLA P LORO 7 OZ. · 90406810000</t>
+          <t>D KT ALIMENTO PARA KOI 25LB · 93500000264</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>90406810000</t>
+          <t>93500000264</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19858,16 +19858,16 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>D KT EGGCITE PERIQUITO 5 LB · 90405910000</t>
+          <t>D KT BARRA DE SEMILLA P LORO 7 OZ. · 90406810000</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>90405910000</t>
+          <t>90406810000</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19878,16 +19878,16 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>D KT EXACT RAINBOW LORO LGE 2.5LB · 90416670000</t>
+          <t>D KT EGGCITE PERIQUITO 5 LB · 90405910000</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>90416670000</t>
+          <t>90405910000</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19898,16 +19898,16 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>D KT FDPH ALIM PARA PERIQUITOS 2LB · 93511590000</t>
+          <t>D KT EXACT RAINBOW LORO LGE 2.5LB · 90416670000</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>93511590000</t>
+          <t>90416670000</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19918,16 +19918,16 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>D KT FDPH ALIM PARA PERIQUITOS 4LB · 93511600000</t>
+          <t>D KT FDPH ALIM PARA PERIQUITOS 2LB · 93511590000</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>93511600000</t>
+          <t>93511590000</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19938,16 +19938,16 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>D KT FDPH SNACK VERDE P/AVES 1OZ · 93506980000</t>
+          <t>D KT FDPH ALIM PARA PERIQUITOS 4LB · 93511600000</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>93506980000</t>
+          <t>93511600000</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19958,16 +19958,16 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>D KT FIESTA SNACK FRUTAS MIXTAS P/ROE · 93507150000</t>
+          <t>D KT FDPH SNACK VERDE P/AVES 1OZ · 93506980000</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>93507150000</t>
+          <t>93506980000</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19978,16 +19978,16 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>D KT SNACK NATURAL HAMSTER/GERBIL 2OZ · 93517200000</t>
+          <t>D KT FIESTA SNACK FRUTAS MIXTAS P/ROE · 93507150000</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>93517200000</t>
+          <t>93507150000</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19998,16 +19998,16 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>KT ALIM EXACT LORO Y CONURO RB 4 LB · 90407280000</t>
+          <t>D KT SNACK NATURAL HAMSTER/GERBIL 2OZ · 93517200000</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>90407280000</t>
+          <t>93517200000</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20018,16 +20018,16 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>KT ALIM FIESTA HAMSTER/GERBIL 2.5LB · 90405280000</t>
+          <t>KT ALIM EXACT LORO Y CONURO RB 4 LB · 90407280000</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>90405280000</t>
+          <t>90407280000</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20038,16 +20038,16 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>KT ALIM FIESTA P PERIQUITO 2 LB · 90404720000</t>
+          <t>KT ALIM FIESTA HAMSTER/GERBIL 2.5LB · 90405280000</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>90404720000</t>
+          <t>90405280000</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20058,16 +20058,16 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>KT ALIM KAYTEE FIESTA CONURO 4.5 LB · 90406700000</t>
+          <t>KT ALIM FIESTA P PERIQUITO 2 LB · 90404720000</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>90406700000</t>
+          <t>90404720000</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20078,12 +20078,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>KT ALIM TIMOTHY COMP P/CONEJOS 4.5 · 93507020000</t>
+          <t>KT ALIM KAYTEE FIESTA CONURO 4.5 LB · 90406700000</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>93507020000</t>
+          <t>90406700000</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -20098,16 +20098,16 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>KT ALIM TIMOTHY SELECT CONEJOS 3.5 · 93518150000</t>
+          <t>KT ALIM TIMOTHY COMP P/CONEJOS 4.5 · 93507020000</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>93518150000</t>
+          <t>93507020000</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20118,16 +20118,16 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
+          <t>KT ALIM TIMOTHY SELECT CONEJOS 3.5 · 93518150000</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>90404930000</t>
+          <t>93518150000</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20138,16 +20138,16 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT PERIQUITO RB 2 LB · 90405940000</t>
+          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>90405940000</t>
+          <t>90404930000</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20158,16 +20158,16 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>KT ALIM. FIESTA MAX CONEJO 3.5LB · 90402840000</t>
+          <t>KT ALIM. EXACT PERIQUITO RB 2 LB · 90405940000</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>90402840000</t>
+          <t>90405940000</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20178,12 +20178,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>KT ALIM. FORTI DIET COBAYO 5 LB · 90407730000</t>
+          <t>KT ALIM. FIESTA MAX CONEJO 3.5LB · 90402840000</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>90407730000</t>
+          <t>90402840000</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -20198,16 +20198,16 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>KT ALIM. FORTI DIET CONEJO 10 LB · 90407390000</t>
+          <t>KT ALIM. FORTI DIET COBAYO 5 LB · 90407730000</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>90407390000</t>
+          <t>90407730000</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20218,16 +20218,16 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>KT ALIM. FORTI DIET CONEJO 5 LB · 90405030000</t>
+          <t>KT ALIM. FORTI DIET CONEJO 10 LB · 90407390000</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>90405030000</t>
+          <t>90407390000</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20238,16 +20238,16 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME COBAYO 5 LB · 90405110000</t>
+          <t>KT ALIM. FORTI DIET CONEJO 5 LB · 90405030000</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>90405110000</t>
+          <t>90405030000</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME CONEJO 10LB · 90407440000</t>
+          <t>KT ALIM. SUPREME COBAYO 5 LB · 90405110000</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>90407440000</t>
+          <t>90405110000</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20278,16 +20278,16 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
+          <t>KT ALIM. SUPREME CONEJO 10LB · 90407440000</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>90405210000</t>
+          <t>90407440000</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20298,16 +20298,16 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME PERIQUITO 5 LB · 90404880000</t>
+          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>90404880000</t>
+          <t>90405210000</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20318,16 +20318,16 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>KT ALIMENTO PARA KOI 10LB · 93500000265</t>
+          <t>KT ALIM. SUPREME PERIQUITO 5 LB · 90404880000</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>93500000265</t>
+          <t>90404880000</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20338,16 +20338,16 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>KT ALIMENTO PARA KOI 3LB · 93500000266</t>
+          <t>KT ALIMENTO PARA KOI 10LB · 93500000265</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>93500000266</t>
+          <t>93500000265</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20358,16 +20358,16 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>KT ALIMENTO TIMOTHY SELECT COBAYA 3 · 93518140000</t>
+          <t>KT ALIMENTO PARA KOI 3LB · 93500000266</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>93518140000</t>
+          <t>93500000266</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20378,16 +20378,16 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>KT BARRA  D SEMILLA P/LORO MIEL 7OZ · 90402120000</t>
+          <t>KT ALIMENTO TIMOTHY SELECT COBAYA 3 · 93518140000</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>90402120000</t>
+          <t>93518140000</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20398,16 +20398,16 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>KT BARRA DE SEMILLA P CONEJO 6OZ. · 90406790000</t>
+          <t>KT BARRA  D SEMILLA P/LORO MIEL 7OZ · 90402120000</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>90406790000</t>
+          <t>90402120000</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20418,12 +20418,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>KT BARRA DE SEMILLA P PERICO 7 OZ · 90406800000</t>
+          <t>KT BARRA DE SEMILLA P CONEJO 6OZ. · 90406790000</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>90406800000</t>
+          <t>90406790000</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -20438,16 +20438,16 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>KT EXACT  LORO LARGE RB  4 LB · 90407300000</t>
+          <t>KT BARRA DE SEMILLA P PERICO 7 OZ · 90406800000</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>90407300000</t>
+          <t>90406800000</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20458,16 +20458,16 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>KT EXACT PARA PICHONES 5 LB · 90407340000</t>
+          <t>KT EXACT  LORO LARGE RB  4 LB · 90407300000</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>90407340000</t>
+          <t>90407300000</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20478,16 +20478,16 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
+          <t>KT EXACT PARA PICHONES 5 LB · 90407340000</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>90404920000</t>
+          <t>90407340000</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20498,16 +20498,16 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>KT FDPH CONURO PERIQUITO 4LB · 93500000608</t>
+          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>93500000608</t>
+          <t>90404920000</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20518,16 +20518,16 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>KT FIESTA MAXI LORO 4.5LB · 90402160000</t>
+          <t>KT FDPH CONURO PERIQUITO 4LB · 93500000608</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>90402160000</t>
+          <t>93500000608</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20538,16 +20538,16 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>KT FIESTA SNACK PAPAYA PEQ. ESP 2.5 · 93507160000</t>
+          <t>KT FIESTA MAXI LORO 4.5LB · 90402160000</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>93507160000</t>
+          <t>90402160000</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20558,16 +20558,16 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>KT FIESTA SNACK YOGURT FRESA/BANANA · 93506900000</t>
+          <t>KT FIESTA SNACK PAPAYA PEQ. ESP 2.5 · 93507160000</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>93506900000</t>
+          <t>93507160000</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20578,16 +20578,16 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>KT FIESTA TROCITOS DE PAPAYA 2.5OZ · 93506770000</t>
+          <t>KT FIESTA SNACK YOGURT FRESA/BANANA · 93506900000</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>93506770000</t>
+          <t>93506900000</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -20598,16 +20598,16 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>KT FORTI DIET PERICO 2 LB · 90404800000</t>
+          <t>KT FIESTA TROCITOS DE PAPAYA 2.5OZ · 93506770000</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>90404800000</t>
+          <t>93506770000</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -20618,16 +20618,16 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>KT FORTI DIET PERICOS 5 LBS · 90400000000</t>
+          <t>KT FORTI DIET PERICO 2 LB · 90404800000</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>90400000000</t>
+          <t>90404800000</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -20638,16 +20638,16 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>KT SNACK FRESA P/ROEDORES 5.5OZ · 93517190000</t>
+          <t>KT FORTI DIET PERICOS 5 LBS · 90400000000</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>93517190000</t>
+          <t>90400000000</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -20658,16 +20658,16 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>KT SNACK NATURAL P/CONEJOS Y COBAYO · 93517210000</t>
+          <t>KT SNACK FRESA P/ROEDORES 5.5OZ · 93517190000</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>93517210000</t>
+          <t>93517190000</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -20678,16 +20678,16 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
+          <t>KT SNACK NATURAL P/CONEJOS Y COBAYO · 93517210000</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>93500800000</t>
+          <t>93517210000</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -20698,36 +20698,36 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>KORDON VITAMINA C PARA COBAYOS 2OZ · 90310300000</t>
+          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>90310300000</t>
+          <t>93500800000</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES PEQUENAS 2 OZ · 90720870000</t>
+          <t>KORDON VITAMINA C PARA COBAYOS 2OZ · 90310300000</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>90720870000</t>
+          <t>90310300000</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -20738,12 +20738,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS PARA REPTILES 2OZ · 90310270000</t>
+          <t>KORDON VITAMINAS AVES PEQUENAS 2 OZ · 90720870000</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>90310270000</t>
+          <t>90720870000</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -20758,36 +20758,36 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>KORDON VITAMINAS PARA REPTILES 2OZ · 90310270000</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>90409680000</t>
+          <t>90310270000</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>KORDON</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>90400360000</t>
+          <t>90409680000</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -20798,16 +20798,16 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>93513340000</t>
+          <t>90400360000</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -20818,16 +20818,16 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>90400340000</t>
+          <t>93513340000</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -20838,16 +20838,16 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>93513280000</t>
+          <t>90400340000</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -20858,32 +20858,32 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>90322660000</t>
+          <t>93513280000</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>M MENU NV VIT MAST/PERRO 32730 X 5U · 93519960000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>93519960000</t>
+          <t>90322660000</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -20891,23 +20891,23 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>NATURVET</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>M MENUDEO NV VITAMINAS 90328320000 · 90326270000</t>
+          <t>M MENU NV VIT MAST/PERRO 32730 X 5U · 93519960000</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>90326270000</t>
+          <t>93519960000</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -20918,36 +20918,36 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>M MENUDEO NV VITAMINAS 90328320000 · 90326270000</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>93510820000</t>
+          <t>90326270000</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NATURVET</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>93510810000</t>
+          <t>93510820000</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -20958,16 +20958,16 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>93505910000</t>
+          <t>93510810000</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -20978,16 +20978,16 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>93505950000</t>
+          <t>93505910000</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -20998,16 +20998,16 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>93505960000</t>
+          <t>93505950000</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -21018,16 +21018,16 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>93505920000</t>
+          <t>93505960000</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -21038,16 +21038,16 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>93505930000</t>
+          <t>93505920000</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -21058,16 +21058,16 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>93505940000</t>
+          <t>93505930000</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -21078,16 +21078,16 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>90410720000</t>
+          <t>93505940000</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -21098,16 +21098,16 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>90410720000</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -21118,16 +21118,16 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>90410970000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -21138,16 +21138,16 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>90410800000</t>
+          <t>90410970000</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -21158,16 +21158,16 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>90410820000</t>
+          <t>90410800000</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -21178,12 +21178,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>90410830000</t>
+          <t>90410820000</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -21198,12 +21198,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>90415960000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -21218,16 +21218,16 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>90410810000</t>
+          <t>90415960000</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -21238,16 +21238,16 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>93510840000</t>
+          <t>90410810000</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -21258,16 +21258,16 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>93510840000</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -21278,32 +21278,32 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>90328330000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
+          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>93518700000</t>
+          <t>90328330000</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -21318,12 +21318,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>D NV SUPLEMEN HONGOS P/SISTEMA INMUNE · 90332570000</t>
+          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>90332570000</t>
+          <t>93518700000</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -21338,16 +21338,16 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>D NV SUPLEMENTO ANTI COPROFAGIA 500 · 90328650000</t>
+          <t>D NV SUPLEMEN HONGOS P/SISTEMA INMUNE · 90332570000</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>90328650000</t>
+          <t>90332570000</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -21358,16 +21358,16 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>D NV SUPLEMENTO TRANQUILIZANTE 180 UD · 93518710000</t>
+          <t>D NV SUPLEMENTO ANTI COPROFAGIA 500 · 90328650000</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>93518710000</t>
+          <t>90328650000</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -21378,12 +21378,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>D NV TABLETAS CON ARANDANOS P/VEJIGA · 90327400000</t>
+          <t>D NV SUPLEMENTO TRANQUILIZANTE 180 UD · 93518710000</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>90327400000</t>
+          <t>93518710000</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -21398,16 +21398,16 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
+          <t>D NV TABLETAS CON ARANDANOS P/VEJIGA · 90327400000</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>90328340000</t>
+          <t>90327400000</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -21418,16 +21418,16 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
+          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>90327410000</t>
+          <t>90328340000</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -21438,12 +21438,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>NV ENZIMAS DIGESTIVAS P/PERROS 70UD · 90327670000</t>
+          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>90327670000</t>
+          <t>90327410000</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -21458,16 +21458,16 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
+          <t>NV ENZIMAS DIGESTIVAS P/PERROS 70UD · 90327670000</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>90327780000</t>
+          <t>90327670000</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -21478,12 +21478,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>90328050000</t>
+          <t>90327780000</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -21498,16 +21498,16 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>NV HIP N JOINT CON OMEGA P/GATO 60U · 90328310000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>90328310000</t>
+          <t>90328050000</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -21518,16 +21518,16 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
+          <t>NV HIP N JOINT CON OMEGA P/GATO 60U · 90328310000</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>90328300000</t>
+          <t>90328310000</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -21538,12 +21538,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/GATO 60 · 90327630000</t>
+          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>90327630000</t>
+          <t>90328300000</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -21558,16 +21558,16 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
+          <t>NV PAST MAST CON ARANDANO P/GATO 60 · 90327630000</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>90327640000</t>
+          <t>90327630000</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -21578,16 +21578,16 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
+          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>90328780000</t>
+          <t>90327640000</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -21598,16 +21598,16 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
+          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>90328700000</t>
+          <t>90328780000</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -21618,12 +21618,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
+          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>90328860000</t>
+          <t>90328700000</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -21638,16 +21638,16 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
+          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>90328840000</t>
+          <t>90328860000</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -21658,16 +21658,16 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>NV VITAMINAS MAST P/PERROS 60 · 90327290000</t>
+          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>90327290000</t>
+          <t>90328840000</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -21678,16 +21678,16 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>NV VITAMINAS PERROS/GATOS 200UD · 90328320000</t>
+          <t>NV VITAMINAS MAST P/PERROS 60 · 90327290000</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>90328320000</t>
+          <t>90327290000</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -21698,12 +21698,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE GF 12LB · 93500000457</t>
+          <t>NV VITAMINAS PERROS/GATOS 200UD · 90328320000</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>93500000457</t>
+          <t>90328320000</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -21711,23 +21711,23 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE GF 4LB · 93500000458</t>
+          <t>NS CACHORRO RZ GDE GF 12LB · 93500000457</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>93500000458</t>
+          <t>93500000457</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -21738,16 +21738,16 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 12LB · 93500000428</t>
+          <t>NS CACHORRO RZ GDE GF 4LB · 93500000458</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>93500000428</t>
+          <t>93500000458</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -21758,16 +21758,16 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 12LB · 93500000428</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>93500000429</t>
+          <t>93500000428</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -21778,16 +21778,16 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>93500000460</t>
+          <t>93500000429</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -21798,16 +21798,16 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>93500000461</t>
+          <t>93500000460</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -21818,12 +21818,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>NS CACHORRO SM MD POLLO Y ARROZ 12LB · 93500000425</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>93500000425</t>
+          <t>93500000461</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -21838,16 +21838,16 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>NS CACHORRO SM MD POLLO Y ARROZ 4LB · 93500000426</t>
+          <t>NS CACHORRO SM MD POLLO Y ARROZ 12LB · 93500000425</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>93500000426</t>
+          <t>93500000425</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -21858,16 +21858,16 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>NS CACHORRO SM MD POLLO Y ARROZ 4LB · 93500000426</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>90034090000</t>
+          <t>93500000426</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -21878,12 +21878,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>90033960000</t>
+          <t>90034090000</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -21898,16 +21898,16 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>90034200000</t>
+          <t>90033960000</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -21918,12 +21918,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
+          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>90034180000</t>
+          <t>90034200000</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -21938,12 +21938,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
+          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>90034290000</t>
+          <t>90034180000</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -21958,12 +21958,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
+          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>90034190000</t>
+          <t>90034290000</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -21978,16 +21978,16 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
+          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>90034130000</t>
+          <t>90034190000</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -21998,16 +21998,16 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
+          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>90034150000</t>
+          <t>90034130000</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -22018,16 +22018,16 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>90034160000</t>
+          <t>90034150000</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -22038,16 +22038,16 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 40LB · 90034010000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>90034010000</t>
+          <t>90034160000</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -22058,16 +22058,16 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
+          <t>NS CHOICE POLLO Y CEBADA 40LB · 90034010000</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>90033990000</t>
+          <t>90034010000</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -22078,16 +22078,16 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>NS CHOICE R GDE CARNE Y CEBADA 40LB · 90034030000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>90034030000</t>
+          <t>90033990000</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
+          <t>NS CHOICE R GDE CARNE Y CEBADA 40LB · 90034030000</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>90034210000</t>
+          <t>90034030000</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -22118,16 +22118,16 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
+          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>90034250000</t>
+          <t>90034210000</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -22138,16 +22138,16 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
+          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>90034230000</t>
+          <t>90034250000</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>NS CTRL PESO PERRO POLLO 12LB · 93500000416</t>
+          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>93500000416</t>
+          <t>90034230000</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -22178,16 +22178,16 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
+          <t>NS CTRL PESO PERRO POLLO 12LB · 93500000416</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>93500000479</t>
+          <t>93500000416</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -22198,16 +22198,16 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>NS GATO Y GATITO POLLO Y ARROZ 4LB · 93500000477</t>
+          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>93500000477</t>
+          <t>93500000479</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -22218,16 +22218,16 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
+          <t>NS GATO Y GATITO POLLO Y ARROZ 4LB · 93500000477</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>93500000469</t>
+          <t>93500000477</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -22238,16 +22238,16 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
+          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>93500000471</t>
+          <t>93500000469</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -22258,16 +22258,16 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>93500000488</t>
+          <t>93500000471</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -22278,16 +22278,16 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
+          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>93500000486</t>
+          <t>93500000488</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -22298,16 +22298,16 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
+          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>93500000487</t>
+          <t>93500000486</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -22318,12 +22318,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
+          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>93500000475</t>
+          <t>93500000487</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -22338,16 +22338,16 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
+          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>93500000472</t>
+          <t>93500000475</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -22358,16 +22358,16 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
+          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>93500000468</t>
+          <t>93500000472</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -22378,16 +22378,16 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
+          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>93500000467</t>
+          <t>93500000468</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -22398,16 +22398,16 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
+          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>93500000473</t>
+          <t>93500000467</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -22418,16 +22418,16 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
+          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>93500000466</t>
+          <t>93500000473</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -22438,16 +22438,16 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>NS LATA SENIOR POLLO 13OZ · 93500000470</t>
+          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>93500000470</t>
+          <t>93500000466</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -22458,16 +22458,16 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
+          <t>NS LATA SENIOR POLLO 13OZ · 93500000470</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>93500000419</t>
+          <t>93500000470</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -22478,16 +22478,16 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>93500000420</t>
+          <t>93500000419</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -22498,16 +22498,16 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>93500000423</t>
+          <t>93500000420</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -22518,12 +22518,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 12LB · 93500000421</t>
+          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>93500000421</t>
+          <t>93500000423</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -22538,16 +22538,16 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 12LB · 93500000421</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>93500000422</t>
+          <t>93500000421</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -22558,16 +22558,16 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>93500000434</t>
+          <t>93500000422</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -22578,16 +22578,16 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 26LB · 93500000436</t>
+          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>93500000436</t>
+          <t>93500000434</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -22598,16 +22598,16 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS PERRO CORDERO Y ARROZ 26LB · 93500000436</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>93500000435</t>
+          <t>93500000436</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -22618,16 +22618,16 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>93500000451</t>
+          <t>93500000435</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -22638,16 +22638,16 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
+          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>93500000452</t>
+          <t>93500000451</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -22658,12 +22658,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>NS PERRO GF CORDERO Y GUISANTES 12LB · 93500000444</t>
+          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>93500000444</t>
+          <t>93500000452</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -22678,16 +22678,16 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
+          <t>NS PERRO GF CORDERO Y GUISANTES 12LB · 93500000444</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>93500000445</t>
+          <t>93500000444</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -22698,16 +22698,16 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
+          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>93500000463</t>
+          <t>93500000445</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -22718,16 +22718,16 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>93500000464</t>
+          <t>93500000463</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -22738,16 +22738,16 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO GUISANTE 12LB · 93500000441</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>93500000441</t>
+          <t>93500000464</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -22758,16 +22758,16 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
+          <t>NS PERRO GF POLLO GUISANTE 12LB · 93500000441</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>93500000442</t>
+          <t>93500000441</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -22778,16 +22778,16 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
+          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>93500000449</t>
+          <t>93500000442</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -22798,12 +22798,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>93500000450</t>
+          <t>93500000449</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -22818,12 +22818,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>93500000438</t>
+          <t>93500000450</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -22838,16 +22838,16 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
+          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>93500000439</t>
+          <t>93500000438</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -22858,16 +22858,16 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
+          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>93500000454</t>
+          <t>93500000439</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -22878,16 +22878,16 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 4LB · 93500000455</t>
+          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>93500000455</t>
+          <t>93500000454</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -22898,16 +22898,16 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
+          <t>NS PERRO SENIOR GF 4LB · 93500000455</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>93500000431</t>
+          <t>93500000455</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -22918,16 +22918,16 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
+          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>93500000432</t>
+          <t>93500000431</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -22938,12 +22938,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
+          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>93500000495</t>
+          <t>93500000432</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -22958,16 +22958,16 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
+          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>93500000496</t>
+          <t>93500000495</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -22978,16 +22978,16 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>NS SNACK GF PEQ BOCADOS CARNE 6OZ · 93500000494</t>
+          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>93500000494</t>
+          <t>93500000496</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -22998,36 +22998,36 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>D NY SNACK DENTAL FILET MIGNON MINI78 · 93513790000</t>
+          <t>NS SNACK GF PEQ BOCADOS CARNE 6OZ · 93500000494</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>93513790000</t>
+          <t>93500000494</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>D NY SNACK DENTAL FILET MIGNON SM 64U · 93504610000</t>
+          <t>D NY SNACK DENTAL FILET MIGNON MINI78 · 93513790000</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>93504610000</t>
+          <t>93513790000</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -23038,12 +23038,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>D NY SNACK RELLENO 4CT · 93500000335</t>
+          <t>D NY SNACK DENTAL FILET MIGNON SM 64U · 93504610000</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>93500000335</t>
+          <t>93504610000</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -23058,16 +23058,16 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>D NY SNACKS MINI PARA PERROS 78U · 93504090000</t>
+          <t>D NY SNACK RELLENO 4CT · 93500000335</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>93504090000</t>
+          <t>93500000335</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -23078,16 +23078,16 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>D NYLABONE HUESO REG CARNE ASADA · 93508290000</t>
+          <t>D NY SNACKS MINI PARA PERROS 78U · 93504090000</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>93508290000</t>
+          <t>93504090000</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -23098,16 +23098,16 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>D NYLABONE HUESO REG PAVO/MANZANA · 93508110000</t>
+          <t>D NYLABONE HUESO REG CARNE ASADA · 93508290000</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>93508110000</t>
+          <t>93508290000</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -23118,16 +23118,16 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>D NYLABONE HUESO WOLF SABOR TOCINO · 93508210000</t>
+          <t>D NYLABONE HUESO REG PAVO/MANZANA · 93508110000</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>93508210000</t>
+          <t>93508110000</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -23138,16 +23138,16 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>M MENUD NY SNACK FILET MIG 9350459 · 93515560000</t>
+          <t>D NYLABONE HUESO WOLF SABOR TOCINO · 93508210000</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>93515560000</t>
+          <t>93508210000</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -23158,16 +23158,16 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>M MENUDEO NY SNACKS MINI 9350441 · 93515550000</t>
+          <t>M MENUD NY SNACK FILET MIG 9350459 · 93515560000</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>93515550000</t>
+          <t>93515560000</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -23178,16 +23178,16 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>NUBZ CALDO CON SABOR JAMÓN 1UD GIGANTE · 90022080000</t>
+          <t>M MENUDEO NY SNACKS MINI 9350441 · 93515550000</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>90022080000</t>
+          <t>93515550000</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -23198,16 +23198,16 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>NUBZ CARNE DE RES CON RELLENO 16UD PQNO · 90022120000</t>
+          <t>NUBZ CALDO CON SABOR JAMÓN 1UD GIGANTE · 90022080000</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>90022120000</t>
+          <t>90022080000</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -23218,16 +23218,16 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>NUBZ CARNE DE RES CON RELLENO 2UD GRD · 90022110000</t>
+          <t>NUBZ CARNE DE RES CON RELLENO 16UD PQNO · 90022120000</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>90022110000</t>
+          <t>90022120000</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -23238,16 +23238,16 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>NUBZ CARNE DE RES CON RELLENO 4UD PQNO · 90022090000</t>
+          <t>NUBZ CARNE DE RES CON RELLENO 2UD GRD · 90022110000</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>90022090000</t>
+          <t>90022110000</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -23258,16 +23258,16 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>NUBZ MANTEQUILLA DE MANI 2UD GRANDE · 90022060000</t>
+          <t>NUBZ CARNE DE RES CON RELLENO 4UD PQNO · 90022090000</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>90022060000</t>
+          <t>90022090000</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -23278,16 +23278,16 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>NUBZ PAVO Y BATATA P CACHORRO 8UD PQNO · 90022140000</t>
+          <t>NUBZ MANTEQUILLA DE MANI 2UD GRANDE · 90022060000</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>90022140000</t>
+          <t>90022060000</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -23298,16 +23298,16 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>NUBZ SABOR BISONTE 4UD PQNO · 90022150000</t>
+          <t>NUBZ PAVO Y BATATA P CACHORRO 8UD PQNO · 90022140000</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>90022150000</t>
+          <t>90022140000</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -23318,16 +23318,16 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>NUBZ SABOR CARNE 1UD EXTRA GRANDE · 90022050000</t>
+          <t>NUBZ SABOR BISONTE 4UD PQNO · 90022150000</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>90022050000</t>
+          <t>90022150000</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -23338,16 +23338,16 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>NUBZ SABOR ROAST BEEF 2 UD JUMBO · 90022040000</t>
+          <t>NUBZ SABOR CARNE 1UD EXTRA GRANDE · 90022050000</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>90022040000</t>
+          <t>90022050000</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -23358,16 +23358,16 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL 1CT · 93500000332</t>
+          <t>NUBZ SABOR ROAST BEEF 2 UD JUMBO · 90022040000</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>93500000332</t>
+          <t>90022040000</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -23378,16 +23378,16 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON LG 20U · 93513760000</t>
+          <t>NY SNACK DENTAL 1CT · 93500000332</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>93513760000</t>
+          <t>93500000332</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -23398,16 +23398,16 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON MED40U · 93504940000</t>
+          <t>NY SNACK DENTAL FILET MIGNON LG 20U · 93513760000</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>93504940000</t>
+          <t>93513760000</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -23418,12 +23418,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
+          <t>NY SNACK DENTAL FILET MIGNON MED40U · 93504940000</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>93504600000</t>
+          <t>93504940000</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -23438,12 +23438,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>NY SNACK RELLENO 12CT · 93500000336</t>
+          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>93500000336</t>
+          <t>93504600000</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -23458,16 +23458,16 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>NY SNACK RELLENO 2CT · 93500000337</t>
+          <t>NY SNACK RELLENO 12CT · 93500000336</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>93500000337</t>
+          <t>93500000336</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -23478,16 +23478,16 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>NY SNACKS MINI PARA PERROS 160U · 93504410000</t>
+          <t>NY SNACK RELLENO 2CT · 93500000337</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>93504410000</t>
+          <t>93500000337</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -23498,16 +23498,16 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>NY SNACKS MINI PARA PERROS 32U · 93504080000</t>
+          <t>NY SNACKS MINI PARA PERROS 160U · 93504410000</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>93504080000</t>
+          <t>93504410000</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -23518,16 +23518,16 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO GDE SABOR VENADO · 93507970000</t>
+          <t>NY SNACKS MINI PARA PERROS 32U · 93504080000</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>93507970000</t>
+          <t>93504080000</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -23538,16 +23538,16 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO MD SABOR BISONTE · 93507930000</t>
+          <t>NYLABONE HUESO GDE SABOR VENADO · 93507970000</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>93507930000</t>
+          <t>93507970000</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -23558,16 +23558,16 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO P/CACHOR CORDERO/MAN · 93508360000</t>
+          <t>NYLABONE HUESO MD SABOR BISONTE · 93507930000</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>93508360000</t>
+          <t>93507930000</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -23578,16 +23578,16 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO P/CACHOR PATATA PAVO · 93508330000</t>
+          <t>NYLABONE HUESO P/CACHOR CORDERO/MAN · 93508360000</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>93508330000</t>
+          <t>93508360000</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -23598,16 +23598,16 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
+          <t>NYLABONE HUESO P/CACHOR PATATA PAVO · 93508330000</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>93508280000</t>
+          <t>93508330000</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -23618,16 +23618,16 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO PETITE SABOR TOCINO · 93508190000</t>
+          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>93508190000</t>
+          <t>93508280000</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -23638,16 +23638,16 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO REG PATATA PAVO · 93508340000</t>
+          <t>NYLABONE HUESO PETITE SABOR TOCINO · 93508190000</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>93508340000</t>
+          <t>93508190000</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -23658,16 +23658,16 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO REGULAR SABOR TOCINO · 93508200000</t>
+          <t>NYLABONE HUESO REG PATATA PAVO · 93508340000</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>93508200000</t>
+          <t>93508340000</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -23678,16 +23678,16 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO SUPER CARNE ASADA · 93508320000</t>
+          <t>NYLABONE HUESO REGULAR SABOR TOCINO · 93508200000</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>93508320000</t>
+          <t>93508200000</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -23698,16 +23698,16 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO SUPER SABOR POLLO · 93508270000</t>
+          <t>NYLABONE HUESO SUPER CARNE ASADA · 93508320000</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>93508270000</t>
+          <t>93508320000</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -23718,16 +23718,16 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO SUPER SABOR TOCINO · 93508230000</t>
+          <t>NYLABONE HUESO SUPER SABOR POLLO · 93508270000</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>93508230000</t>
+          <t>93508270000</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -23738,16 +23738,16 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO TRIPLE P/CACHORRO · 93508370000</t>
+          <t>NYLABONE HUESO SUPER SABOR TOCINO · 93508230000</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>93508370000</t>
+          <t>93508230000</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -23758,16 +23758,16 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO WOLF CARNE ASADA · 93508300000</t>
+          <t>NYLABONE HUESO TRIPLE P/CACHORRO · 93508370000</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>93508300000</t>
+          <t>93508370000</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -23778,16 +23778,16 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO WOLF SABOR POLLO · 93508250000</t>
+          <t>NYLABONE HUESO WOLF CARNE ASADA · 93508300000</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>93508250000</t>
+          <t>93508300000</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -23798,36 +23798,36 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>OLA CANARIOS 800GRS · 90405520000</t>
+          <t>NYLABONE HUESO WOLF SABOR POLLO · 93508250000</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>90405520000</t>
+          <t>93508250000</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>OLA COBAYOS 800GRS. · 90405610000</t>
+          <t>OLA CANARIOS 800GRS · 90405520000</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>90405610000</t>
+          <t>90405520000</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -23838,16 +23838,16 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
+          <t>OLA COBAYOS 800GRS. · 90405610000</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>90405540000</t>
+          <t>90405610000</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -23858,36 +23858,36 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>PEDIGREE ADULTO 2KG · 90300120000</t>
+          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>90300120000</t>
+          <t>90405540000</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>PEDIGREE</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>PEDIGREE CACHORRO 2KG · 90300140000</t>
+          <t>PEDIGREE ADULTO 2KG · 90300120000</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>90300140000</t>
+          <t>90300120000</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -23898,16 +23898,16 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>PEDIGREE CACHORRO 4KG · 90320010000</t>
+          <t>PEDIGREE CACHORRO 2KG · 90300140000</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>90320010000</t>
+          <t>90300140000</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -23918,16 +23918,16 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA  CHOICE CUTS BEEF 375 · 90413790000</t>
+          <t>PEDIGREE CACHORRO 4KG · 90320010000</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>90413790000</t>
+          <t>90320010000</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -23938,16 +23938,16 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA CACHORRO 375GR · 90408540000</t>
+          <t>PEDIGREE LATA  CHOICE CUTS BEEF 375 · 90413790000</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>90408540000</t>
+          <t>90413790000</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -23958,16 +23958,16 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA CHOPPED BEEF 375GR · 90408530000</t>
+          <t>PEDIGREE LATA CACHORRO 375GR · 90408540000</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>90408530000</t>
+          <t>90408540000</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -23978,16 +23978,16 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA CHOPPED CHICKEN 375GR · 90408560000</t>
+          <t>PEDIGREE LATA CHOPPED BEEF 375GR · 90408530000</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>90408560000</t>
+          <t>90408530000</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -23998,16 +23998,16 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
+          <t>PEDIGREE LATA CHOPPED CHICKEN 375GR · 90408560000</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>93509400000</t>
+          <t>90408560000</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -24018,16 +24018,16 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
+          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>93509410000</t>
+          <t>93509400000</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -24038,16 +24038,16 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH RES ADULTO 100GR · 93509420000</t>
+          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>93509420000</t>
+          <t>93509410000</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -24058,16 +24058,16 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZA PEQ POUCH POLLO 100GR · 93512280000</t>
+          <t>PEDIGREE POUCH RES ADULTO 100GR · 93509420000</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>93512280000</t>
+          <t>93509420000</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -24078,16 +24078,16 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZA PEQ POUCH RES 100GR · 93512290000</t>
+          <t>PEDIGREE RAZA PEQ POUCH POLLO 100GR · 93512280000</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>93512290000</t>
+          <t>93512280000</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -24098,16 +24098,16 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZAS PEQUENAS 2KG · 90407740000</t>
+          <t>PEDIGREE RAZA PEQ POUCH RES 100GR · 93512290000</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>90407740000</t>
+          <t>93512290000</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -24118,16 +24118,16 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZAS PEQUENAS 4KG · 90415740000</t>
+          <t>PEDIGREE RAZAS PEQUENAS 2KG · 90407740000</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>90415740000</t>
+          <t>90407740000</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -24138,12 +24138,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>PEDIGREE RAZAS PEQUENAS 4KG · 90415740000</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>93502370000</t>
+          <t>90415740000</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -24151,43 +24151,43 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>PEDIGREE</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>D PF CARE CHEWZ ENROLLADO/COLAGENO 2U · 93517870000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>93517870000</t>
+          <t>93502370000</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PERKY PET</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>D PF CARE CHEWZ TWIST/COLAGENO 2UD · 93517830000</t>
+          <t>D PF CARE CHEWZ ENROLLADO/COLAGENO 2U · 93517870000</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>93517830000</t>
+          <t>93517870000</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -24198,12 +24198,12 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>D PF CARE CHEWZ WRAP/COLAGENO POLLO · 93517860000</t>
+          <t>D PF CARE CHEWZ TWIST/COLAGENO 2UD · 93517830000</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>93517860000</t>
+          <t>93517830000</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -24218,16 +24218,16 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>D PF CARNAZA ENROLLADA SABOR MANZANA · 93518230000</t>
+          <t>D PF CARE CHEWZ WRAP/COLAGENO POLLO · 93517860000</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>93518230000</t>
+          <t>93517860000</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -24238,16 +24238,16 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>D PF CARNAZA ENROLLADA SABOR MENTA 4U · 93518210000</t>
+          <t>D PF CARNAZA ENROLLADA SABOR MANZANA · 93518230000</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>93518210000</t>
+          <t>93518230000</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -24258,16 +24258,16 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>D PF HUESO/ CARNAZA SABOR NATUR 11-12 · 93514350000</t>
+          <t>D PF CARNAZA ENROLLADA SABOR MENTA 4U · 93518210000</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>93514350000</t>
+          <t>93518210000</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -24278,16 +24278,16 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>D PF LAZO DE CARNAZA SABOR MANZANA 2U · 93518240000</t>
+          <t>D PF HUESO/ CARNAZA SABOR NATUR 11-12 · 93514350000</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>93518240000</t>
+          <t>93514350000</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -24298,16 +24298,16 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>D PF LAZO DE CARNAZA SABOR MENTA 2UD · 93518220000</t>
+          <t>D PF LAZO DE CARNAZA SABOR MANZANA 2U · 93518240000</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>93518220000</t>
+          <t>93518240000</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -24318,16 +24318,16 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>D PF ROLLO/ CARNAZA SABOR CARNE 10IN · 93514190000</t>
+          <t>D PF LAZO DE CARNAZA SABOR MENTA 2UD · 93518220000</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>93514190000</t>
+          <t>93518220000</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -24338,16 +24338,16 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>D PF ROLLO/ CARNAZA SABOR M.MANI 8IN · 93514300000</t>
+          <t>D PF ROLLO/ CARNAZA SABOR CARNE 10IN · 93514190000</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>93514300000</t>
+          <t>93514190000</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -24358,16 +24358,16 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>PF CARE CHEWZ ENROLLADO/COLAGENO 4U · 93517850000</t>
+          <t>D PF ROLLO/ CARNAZA SABOR M.MANI 8IN · 93514300000</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>93517850000</t>
+          <t>93514300000</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>PF CARE CHEWZ TRENZA/COLAGENO POLLO · 93517810000</t>
+          <t>PF CARE CHEWZ ENROLLADO/COLAGENO 4U · 93517850000</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>93517810000</t>
+          <t>93517850000</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -24398,16 +24398,16 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>PF CARE CHEWZ TRENZA/COLAGENO SM · 93517840000</t>
+          <t>PF CARE CHEWZ TRENZA/COLAGENO POLLO · 93517810000</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>93517840000</t>
+          <t>93517810000</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -24418,16 +24418,16 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>PF CARE CHEWZ TWIST/COLAGENO POLLO · 93517820000</t>
+          <t>PF CARE CHEWZ TRENZA/COLAGENO SM · 93517840000</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>93517820000</t>
+          <t>93517840000</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -24438,16 +24438,16 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>PF CARECHEWZ COLAGENO ENROLL POLLO · 93517800000</t>
+          <t>PF CARE CHEWZ TWIST/COLAGENO POLLO · 93517820000</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>93517800000</t>
+          <t>93517820000</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -24458,16 +24458,16 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR CARNE 6-7IN · 93514170000</t>
+          <t>PF CARECHEWZ COLAGENO ENROLL POLLO · 93517800000</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>93514170000</t>
+          <t>93517800000</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -24478,16 +24478,16 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR CARNE 8-9IN · 93514180000</t>
+          <t>PF HUESO/ CARNAZA SABOR CARNE 6-7IN · 93514170000</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>93514180000</t>
+          <t>93514170000</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -24498,16 +24498,16 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 6-7IN · 93514270000</t>
+          <t>PF HUESO/ CARNAZA SABOR CARNE 8-9IN · 93514180000</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>93514270000</t>
+          <t>93514180000</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -24518,16 +24518,16 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 6-7IN · 93514270000</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>93514280000</t>
+          <t>93514270000</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -24538,16 +24538,16 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATU 13-15 · 93514360000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>93514360000</t>
+          <t>93514280000</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -24558,16 +24558,16 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATU 15-17 · 93514370000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATU 13-15 · 93514360000</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>93514370000</t>
+          <t>93514360000</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -24578,16 +24578,16 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATURA 5-6IN · 93514320000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATU 15-17 · 93514370000</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>93514320000</t>
+          <t>93514370000</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -24598,16 +24598,16 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATURA 7-8IN · 93514330000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATURA 5-6IN · 93514320000</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>93514330000</t>
+          <t>93514320000</t>
         </is>
       </c>
       <c r="C553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -24618,16 +24618,16 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATURA 9-10 · 93514340000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATURA 7-8IN · 93514330000</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>93514340000</t>
+          <t>93514330000</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -24638,12 +24638,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 6-7IN · 93514220000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATURA 9-10 · 93514340000</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>93514220000</t>
+          <t>93514340000</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -24658,16 +24658,16 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 6-7IN · 93514220000</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>93514230000</t>
+          <t>93514220000</t>
         </is>
       </c>
       <c r="C556" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -24678,16 +24678,16 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR CARNE 8IN · 93514200000</t>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>93514200000</t>
+          <t>93514230000</t>
         </is>
       </c>
       <c r="C557" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -24698,16 +24698,16 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR M.MANI 10IN · 93514290000</t>
+          <t>PF ROLLO/ CARNAZA SABOR CARNE 8IN · 93514200000</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>93514290000</t>
+          <t>93514200000</t>
         </is>
       </c>
       <c r="C558" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -24718,16 +24718,16 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
+          <t>PF ROLLO/ CARNAZA SABOR M.MANI 10IN · 93514290000</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>93514240000</t>
+          <t>93514290000</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -24738,16 +24738,16 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR POLLO 8IN · 93514250000</t>
+          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>93514250000</t>
+          <t>93514240000</t>
         </is>
       </c>
       <c r="C560" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -24758,16 +24758,16 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>PF ROLLO/CARNAZA SABOR CARNE 5IN · 93517710000</t>
+          <t>PF ROLLO/ CARNAZA SABOR POLLO 8IN · 93514250000</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>93517710000</t>
+          <t>93514250000</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -24778,16 +24778,16 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>PF ROLLO/CARNAZA SABOR M.MANI 5IN · 93517750000</t>
+          <t>PF ROLLO/CARNAZA SABOR CARNE 5IN · 93517710000</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>93517750000</t>
+          <t>93517710000</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -24798,16 +24798,16 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>PF ROLLO/CARNAZA SABOR NATURAL 10IN · 93517740000</t>
+          <t>PF ROLLO/CARNAZA SABOR M.MANI 5IN · 93517750000</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>93517740000</t>
+          <t>93517750000</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -24818,16 +24818,16 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>PF TRENZA/CARNAZA SABOR NATURAL 12IN · 93517770000</t>
+          <t>PF ROLLO/CARNAZA SABOR NATURAL 10IN · 93517740000</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>93517770000</t>
+          <t>93517740000</t>
         </is>
       </c>
       <c r="C564" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -24838,16 +24838,16 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
+          <t>PF TRENZA/CARNAZA SABOR NATURAL 12IN · 93517770000</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>93517760000</t>
+          <t>93517770000</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -24858,36 +24858,36 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>PD GATO PRESC MULTICARE 4LB · 90411220000</t>
+          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>90411220000</t>
+          <t>93517760000</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>PRESCRIPTION DIET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
+          <t>PD GATO PRESC MULTICARE 4LB · 90411220000</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>90304010000</t>
+          <t>90411220000</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -24898,12 +24898,12 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>SD CANINE W/D DRY 8.5LBS · 90310080000</t>
+          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>90310080000</t>
+          <t>90304010000</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -24918,16 +24918,16 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>SD CANINE/FELINE A/D 5.5 OZ. · 90304470000</t>
+          <t>SD CANINE W/D DRY 8.5LBS · 90310080000</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>90304470000</t>
+          <t>90310080000</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -24938,12 +24938,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
+          <t>SD CANINE/FELINE A/D 5.5 OZ. · 90304470000</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>90406520000</t>
+          <t>90304470000</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -24958,16 +24958,16 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>SD LATA CANINE K/D12/ 13 OZ. · 90406540000</t>
+          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>90406540000</t>
+          <t>90406520000</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -24978,16 +24978,16 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
+          <t>SD LATA CANINE K/D12/ 13 OZ. · 90406540000</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>90406480000</t>
+          <t>90406540000</t>
         </is>
       </c>
       <c r="C572" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -24998,16 +24998,16 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>SD PD CANIN H/D 3.3LB · 93516950000</t>
+          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>93516950000</t>
+          <t>90406480000</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -25018,16 +25018,16 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
+          <t>SD PD CANIN H/D 3.3LB · 93516950000</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>93517100000</t>
+          <t>93516950000</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -25038,16 +25038,16 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
+          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>93517060000</t>
+          <t>93517100000</t>
         </is>
       </c>
       <c r="C575" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -25058,36 +25058,36 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
+          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>93500000100</t>
+          <t>93517060000</t>
         </is>
       </c>
       <c r="C576" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRESCRIPTION DIET</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
+          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>93500000200</t>
+          <t>93500000100</t>
         </is>
       </c>
       <c r="C577" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -25098,16 +25098,16 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>PRO PET 10KG ADULTO · 93500000500</t>
+          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>93500000500</t>
+          <t>93500000200</t>
         </is>
       </c>
       <c r="C578" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -25118,12 +25118,12 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>PRO PET 18KG ADULTO · 93500000600</t>
+          <t>PRO PET 10KG ADULTO · 93500000500</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>93500000600</t>
+          <t>93500000500</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -25138,12 +25138,12 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>PRO PET 4KG ADULTO · 93500000300</t>
+          <t>PRO PET 18KG ADULTO · 93500000600</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>93500000300</t>
+          <t>93500000600</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -25158,16 +25158,16 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>93500000400</t>
+          <t>93500000300</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -25178,36 +25178,36 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>90009650000</t>
+          <t>93500000400</t>
         </is>
       </c>
       <c r="C582" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>PP ADULTO RZ PEQUENA OPTI 7.5KG · 93501251000</t>
+          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>93501251000</t>
+          <t>90009650000</t>
         </is>
       </c>
       <c r="C583" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -25218,16 +25218,16 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
+          <t>PP ADULTO RZ PEQUENA OPTI 7.5KG · 93501251000</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>93510171000</t>
+          <t>93501251000</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -25238,16 +25238,16 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  MD/G 13KG · 93510181000</t>
+          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>93510181000</t>
+          <t>93510171000</t>
         </is>
       </c>
       <c r="C585" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -25258,16 +25258,16 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>PP CACHORRO RZ GRANDE 3.5KG · 93501121000</t>
+          <t>PP ADULTO SENSITIVE SKIN  MD/G 13KG · 93510181000</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>93501121000</t>
+          <t>93510181000</t>
         </is>
       </c>
       <c r="C586" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -25278,16 +25278,16 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>PP GATO ADULTO SALMON 85G · 90403691000</t>
+          <t>PP CACHORRO RZ GRANDE 3.5KG · 93501121000</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>90403691000</t>
+          <t>93501121000</t>
         </is>
       </c>
       <c r="C587" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -25298,16 +25298,16 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
+          <t>PP GATO ADULTO SALMON 85G · 90403691000</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>90401421000</t>
+          <t>90403691000</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -25318,16 +25318,16 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
+          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>93519420000</t>
+          <t>90401421000</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -25338,16 +25338,16 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>93519430000</t>
+          <t>93519420000</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -25358,16 +25358,16 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>93519440000</t>
+          <t>93519430000</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -25378,16 +25378,16 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>93519410000</t>
+          <t>93519440000</t>
         </is>
       </c>
       <c r="C592" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -25398,16 +25398,16 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>93519460000</t>
+          <t>93519410000</t>
         </is>
       </c>
       <c r="C593" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -25418,16 +25418,16 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>93519450000</t>
+          <t>93519460000</t>
         </is>
       </c>
       <c r="C594" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -25438,16 +25438,16 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>PP KITTEN 85G · 90401190000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>90401190000</t>
+          <t>93519450000</t>
         </is>
       </c>
       <c r="C595" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -25458,16 +25458,16 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP KITTEN 85G · 90401190000</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>93519470000</t>
+          <t>90401190000</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         </is>
       </c>
       <c r="C693" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         </is>
       </c>
       <c r="C780" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         </is>
       </c>
       <c r="C821" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         </is>
       </c>
       <c r="C823" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         </is>
       </c>
       <c r="C824" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>
